--- a/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>OCEA</t>
   </si>
@@ -664,10 +664,11 @@
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
@@ -697,16 +698,16 @@
         <v>44926</v>
       </c>
       <c r="G7" s="2">
-        <v>44834</v>
+        <v>44742</v>
       </c>
       <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
-        <v>44561</v>
+      <c r="I7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K7" s="2">
         <v>44469</v>
@@ -855,20 +856,20 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3200</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -932,13 +933,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>13600</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -946,11 +947,11 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1020,26 +1021,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>18800</v>
       </c>
       <c r="F17" s="3">
-        <v>600</v>
+        <v>16100</v>
       </c>
       <c r="G17" s="3">
-        <v>1400</v>
+        <v>6900</v>
       </c>
       <c r="H17" s="3">
-        <v>300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>500</v>
+        <v>5100</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -1061,23 +1062,23 @@
       <c r="D18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+      <c r="E18" s="3">
+        <v>-18800</v>
       </c>
       <c r="F18" s="3">
-        <v>-600</v>
+        <v>-16100</v>
       </c>
       <c r="G18" s="3">
-        <v>-1400</v>
+        <v>-6900</v>
       </c>
       <c r="H18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-500</v>
+        <v>-5100</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -1115,23 +1116,23 @@
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+      <c r="E20" s="3">
+        <v>-47000</v>
       </c>
       <c r="F20" s="3">
-        <v>1000</v>
+        <v>-1200</v>
       </c>
       <c r="G20" s="3">
-        <v>400</v>
+        <v>-400</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1156,17 +1157,17 @@
       <c r="E21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="3">
-        <v>400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-200</v>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1188,20 +1189,20 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>300</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1226,26 +1227,26 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-67400</v>
       </c>
       <c r="F23" s="3">
-        <v>400</v>
+        <v>-17400</v>
       </c>
       <c r="G23" s="3">
-        <v>-1000</v>
+        <v>-7300</v>
       </c>
       <c r="H23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-500</v>
+        <v>-5400</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>0</v>
@@ -1340,26 +1341,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-67400</v>
       </c>
       <c r="F26" s="3">
-        <v>400</v>
+        <v>-17400</v>
       </c>
       <c r="G26" s="3">
-        <v>-1000</v>
+        <v>-7300</v>
       </c>
       <c r="H26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-500</v>
+        <v>-5400</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -1378,26 +1379,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-67400</v>
       </c>
       <c r="F27" s="3">
-        <v>400</v>
+        <v>-17400</v>
       </c>
       <c r="G27" s="3">
-        <v>-1000</v>
+        <v>-7300</v>
       </c>
       <c r="H27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-500</v>
+        <v>-5400</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -1571,23 +1572,23 @@
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+      <c r="E32" s="3">
+        <v>47000</v>
       </c>
       <c r="F32" s="3">
-        <v>-1000</v>
+        <v>1200</v>
       </c>
       <c r="G32" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1606,26 +1607,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-67400</v>
       </c>
       <c r="F33" s="3">
-        <v>400</v>
+        <v>-17400</v>
       </c>
       <c r="G33" s="3">
-        <v>-1000</v>
+        <v>-7300</v>
       </c>
       <c r="H33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-500</v>
+        <v>-5400</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -1682,26 +1683,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-67400</v>
       </c>
       <c r="F35" s="3">
-        <v>400</v>
+        <v>-17400</v>
       </c>
       <c r="G35" s="3">
-        <v>-1000</v>
+        <v>-7300</v>
       </c>
       <c r="H35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-500</v>
+        <v>-5400</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -1735,16 +1736,16 @@
         <v>44926</v>
       </c>
       <c r="G38" s="2">
-        <v>44834</v>
+        <v>44742</v>
       </c>
       <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
-        <v>44561</v>
+      <c r="I38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K38" s="2">
         <v>44469</v>
@@ -1798,23 +1799,23 @@
       <c r="D41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
-        <v>500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>800</v>
-      </c>
-      <c r="J41" s="3">
-        <v>1100</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>1200</v>
@@ -1871,26 +1872,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1950,23 +1951,23 @@
       <c r="D45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>700</v>
@@ -1991,20 +1992,20 @@
       <c r="E46" s="3">
         <v>300</v>
       </c>
-      <c r="F46" s="3">
-        <v>500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>600</v>
-      </c>
-      <c r="H46" s="3">
-        <v>700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>1500</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>1800</v>
@@ -2024,25 +2025,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>24700</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2213,26 +2214,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>110400</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>108500</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>107800</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>107100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>107100</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>107100</v>
@@ -2295,20 +2296,20 @@
       <c r="E54" s="3">
         <v>25000</v>
       </c>
-      <c r="F54" s="3">
-        <v>110900</v>
-      </c>
-      <c r="G54" s="3">
-        <v>109100</v>
-      </c>
-      <c r="H54" s="3">
-        <v>108600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>108300</v>
-      </c>
-      <c r="J54" s="3">
-        <v>108700</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>108900</v>
@@ -2359,26 +2360,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3">
-        <v>300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2397,17 +2398,17 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1100</v>
+      <c r="D58" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2435,26 +2436,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
+      <c r="D59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -2479,20 +2480,20 @@
       <c r="E60" s="3">
         <v>23400</v>
       </c>
-      <c r="F60" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>200</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2549,26 +2550,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>2600</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3200</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>3200</v>
@@ -2704,23 +2705,23 @@
       <c r="D66" s="3">
         <v>29300</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3">
-        <v>6600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>5200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I66" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3400</v>
+      <c r="E66" s="3">
+        <v>23400</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>3200</v>
@@ -2908,25 +2909,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-170400</v>
+        <v>-162000</v>
       </c>
       <c r="E72" s="3">
         <v>-149000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-600</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -3059,26 +3060,26 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3">
-        <v>104300</v>
-      </c>
-      <c r="G76" s="3">
-        <v>103900</v>
-      </c>
-      <c r="H76" s="3">
-        <v>104900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>105100</v>
-      </c>
-      <c r="J76" s="3">
-        <v>105300</v>
+      <c r="D76" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>105800</v>
@@ -3150,16 +3151,16 @@
         <v>44926</v>
       </c>
       <c r="G80" s="2">
-        <v>44834</v>
+        <v>44742</v>
       </c>
       <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
-        <v>44561</v>
+      <c r="I80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K80" s="2">
         <v>44469</v>
@@ -3178,26 +3179,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-67400</v>
       </c>
       <c r="F81" s="3">
-        <v>400</v>
+        <v>-17400</v>
       </c>
       <c r="G81" s="3">
-        <v>-1000</v>
+        <v>-7300</v>
       </c>
       <c r="H81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-500</v>
+        <v>-5400</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>0</v>
@@ -3460,26 +3461,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2700</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G89" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="H89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-100</v>
+        <v>-400</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3628,23 +3629,23 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -3834,26 +3835,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2900</v>
       </c>
       <c r="F100" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G100" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="H100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3910,26 +3911,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
       </c>
       <c r="F102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-100</v>
+        <v>200</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>OCEA</t>
   </si>
@@ -656,73 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -759,8 +763,11 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,8 +804,11 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,32 +864,33 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
-        <v>8400</v>
-      </c>
       <c r="G12" s="3">
+        <v>200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I12" s="3">
         <v>3200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -889,8 +903,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,34 +944,37 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
-        <v>13600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="F14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -965,8 +985,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1026,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,46 +1042,50 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="E17" s="3">
-        <v>18800</v>
+        <v>3700</v>
       </c>
       <c r="F17" s="3">
-        <v>16100</v>
+        <v>19300</v>
       </c>
       <c r="G17" s="3">
+        <v>900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I17" s="3">
         <v>6900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
+      <c r="K17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1063,37 +1093,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>-18800</v>
+        <v>-3700</v>
       </c>
       <c r="F18" s="3">
-        <v>-16100</v>
+        <v>-19300</v>
       </c>
       <c r="G18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0</v>
+      <c r="K18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1141,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1117,48 +1151,51 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>-47000</v>
+        <v>-7000</v>
       </c>
       <c r="F20" s="3">
-        <v>-1200</v>
+        <v>-52500</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+      <c r="E21" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-71800</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1184,84 +1221,93 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-13000</v>
+        <v>-14100</v>
       </c>
       <c r="E23" s="3">
-        <v>-67400</v>
+        <v>-11400</v>
       </c>
       <c r="F23" s="3">
-        <v>-17400</v>
+        <v>-72100</v>
       </c>
       <c r="G23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-7300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5400</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
+      <c r="K23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1344,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-13000</v>
+        <v>-14100</v>
       </c>
       <c r="E26" s="3">
-        <v>-67400</v>
+        <v>-11400</v>
       </c>
       <c r="F26" s="3">
-        <v>-17400</v>
+        <v>-72100</v>
       </c>
       <c r="G26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-5400</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
+      <c r="K26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-13000</v>
+        <v>-14100</v>
       </c>
       <c r="E27" s="3">
-        <v>-67400</v>
+        <v>-11400</v>
       </c>
       <c r="F27" s="3">
-        <v>-17400</v>
+        <v>-72100</v>
       </c>
       <c r="G27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-5400</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
+      <c r="K27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>0</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1549,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1631,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1573,75 +1643,81 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>47000</v>
+        <v>7000</v>
       </c>
       <c r="F32" s="3">
-        <v>1200</v>
+        <v>52500</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-13000</v>
+        <v>-14100</v>
       </c>
       <c r="E33" s="3">
-        <v>-67400</v>
+        <v>-11400</v>
       </c>
       <c r="F33" s="3">
-        <v>-17400</v>
+        <v>-72100</v>
       </c>
       <c r="G33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5400</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
+      <c r="K33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-13000</v>
+        <v>-14100</v>
       </c>
       <c r="E35" s="3">
-        <v>-67400</v>
+        <v>-11400</v>
       </c>
       <c r="F35" s="3">
-        <v>-17400</v>
+        <v>-72100</v>
       </c>
       <c r="G35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5400</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
+      <c r="K35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,20 +1877,21 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,20 +1904,23 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,8 +1957,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1893,20 +1986,23 @@
       <c r="J43" s="3">
         <v>0</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1943,8 +2039,11 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1952,10 +2051,10 @@
         <v>1000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1969,32 +2068,35 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>300</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,46 +2109,49 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>1800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>24700</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2057,8 +2162,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2095,8 +2203,11 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2133,8 +2244,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,8 +2326,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2236,19 +2356,22 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>107100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,19 +2408,22 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>20900</v>
+        <v>1000</v>
       </c>
       <c r="E54" s="3">
-        <v>25000</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
+        <v>2200</v>
+      </c>
+      <c r="F54" s="3">
+        <v>300</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2311,20 +2437,23 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>108900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,19 +2485,20 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12100</v>
+        <v>15400</v>
       </c>
       <c r="E57" s="3">
-        <v>13200</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>14000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>15200</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2381,11 +2512,11 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -2393,20 +2524,23 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E58" s="3">
         <v>11900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7100</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2431,19 +2565,22 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="E59" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+        <v>4000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1500</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2457,11 +2594,11 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -2469,19 +2606,22 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>26700</v>
+        <v>30900</v>
       </c>
       <c r="E60" s="3">
-        <v>23400</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
+        <v>29800</v>
+      </c>
+      <c r="F60" s="3">
+        <v>23700</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2495,11 +2635,11 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
@@ -2507,8 +2647,11 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2545,19 +2688,22 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+        <v>45400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>31300</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2571,20 +2717,23 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>3200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,19 +2852,22 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29300</v>
+        <v>76300</v>
       </c>
       <c r="E66" s="3">
-        <v>23400</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+        <v>63800</v>
+      </c>
+      <c r="F66" s="3">
+        <v>55100</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2723,20 +2881,23 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,19 +3074,22 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-162000</v>
+        <v>-179200</v>
       </c>
       <c r="E72" s="3">
-        <v>-149000</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+        <v>-165100</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-153700</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2929,11 +3103,11 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
+        <v>0</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
@@ -2941,8 +3115,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,19 +3238,22 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-8400</v>
+        <v>-75200</v>
       </c>
       <c r="E76" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
+        <v>-61700</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-54800</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -3081,20 +3267,23 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>105800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-13000</v>
+        <v>-14100</v>
       </c>
       <c r="E81" s="3">
-        <v>-67400</v>
+        <v>-11400</v>
       </c>
       <c r="F81" s="3">
-        <v>-17400</v>
+        <v>-72100</v>
       </c>
       <c r="G81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5400</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
+      <c r="K81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>0</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,8 +3426,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3266,8 +3465,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,31 +3670,34 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2700</v>
       </c>
-      <c r="F89" s="3">
-        <v>-1000</v>
-      </c>
       <c r="G89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="I89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3494,8 +3711,11 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,8 +3730,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3548,8 +3769,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,8 +3851,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3650,20 +3880,23 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +3911,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3716,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,32 +4073,35 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>6600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2900</v>
       </c>
-      <c r="F100" s="3">
-        <v>1000</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>200</v>
+      </c>
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +4114,11 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3906,32 +4155,35 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3942,6 +4194,9 @@
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>OCEA</t>
   </si>
@@ -656,100 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -766,8 +769,11 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,34 +877,35 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
       <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>3200</v>
       </c>
       <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
+      <c r="K12" s="3">
+        <v>3200</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
@@ -906,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,37 +963,40 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>14000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -988,8 +1007,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2900</v>
+        <v>-700</v>
       </c>
       <c r="E17" s="3">
-        <v>3700</v>
+        <v>2700</v>
       </c>
       <c r="F17" s="3">
-        <v>19300</v>
+        <v>2800</v>
       </c>
       <c r="G17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
+      <c r="L17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>700</v>
       </c>
       <c r="E18" s="3">
-        <v>-3700</v>
+        <v>-2700</v>
       </c>
       <c r="F18" s="3">
-        <v>-19300</v>
+        <v>-2800</v>
       </c>
       <c r="G18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
+      <c r="L18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,72 +1174,76 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>17000</v>
       </c>
       <c r="E20" s="3">
-        <v>-7000</v>
+        <v>10900</v>
       </c>
       <c r="F20" s="3">
-        <v>-52500</v>
+        <v>7000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="H20" s="3">
-        <v>-400</v>
+        <v>-1100</v>
       </c>
       <c r="I20" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-16400</v>
       </c>
       <c r="E21" s="3">
-        <v>-10800</v>
+        <v>-13600</v>
       </c>
       <c r="F21" s="3">
-        <v>-71800</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-9900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-57800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1224,113 +1260,122 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-72100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5400</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
+      <c r="L23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1347,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-72100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
+      <c r="L26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M26" s="3">
         <v>0</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-72100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
+      <c r="L27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-17000</v>
       </c>
       <c r="E32" s="3">
-        <v>7000</v>
+        <v>-10900</v>
       </c>
       <c r="F32" s="3">
-        <v>52500</v>
+        <v>-7000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-52500</v>
       </c>
       <c r="H32" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="I32" s="3">
-        <v>400</v>
+        <v>-400</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-72100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
+      <c r="L33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-72100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
+      <c r="L35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,8 +1963,9 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1887,19 +1973,19 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>100</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1907,20 +1993,23 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1960,72 +2049,78 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
+      <c r="L43" s="3">
+        <v>0</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2042,69 +2137,75 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>300</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
+      <c r="H46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1100</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -2112,49 +2213,52 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+        <v>3400</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2165,31 +2269,34 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2206,8 +2313,11 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2247,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>107100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,28 +2533,31 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>300</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
+      <c r="H54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>1100</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2440,20 +2565,23 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>108900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,28 +2615,29 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15400</v>
+        <v>900</v>
       </c>
       <c r="E57" s="3">
-        <v>14000</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>15200</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+        <v>1600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1900</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
+      <c r="I57" s="3">
+        <v>10000</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2515,11 +2645,11 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2527,31 +2657,34 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12100</v>
+        <v>13100</v>
       </c>
       <c r="E58" s="3">
-        <v>11900</v>
+        <v>13300</v>
       </c>
       <c r="F58" s="3">
-        <v>7100</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>13100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2568,19 +2701,22 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3400</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="F59" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2597,11 +2733,11 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
@@ -2609,28 +2745,31 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E60" s="3">
         <v>30900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23700</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
+      <c r="H60" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I60" s="3">
+        <v>11000</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2638,11 +2777,11 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
@@ -2650,19 +2789,22 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2691,23 +2833,26 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>45400</v>
+        <v>62100</v>
       </c>
       <c r="E62" s="3">
-        <v>34000</v>
+        <v>41600</v>
       </c>
       <c r="F62" s="3">
+        <v>30500</v>
+      </c>
+      <c r="G62" s="3">
         <v>31300</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2720,20 +2865,23 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,28 +3009,31 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>96300</v>
+      </c>
+      <c r="E66" s="3">
         <v>76300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55100</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+      <c r="H66" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>11000</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2884,20 +3041,23 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,28 +3247,31 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-196100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-179200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-165100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-153700</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3">
+        <v>-81600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-80600</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -3106,11 +3279,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
@@ -3118,8 +3291,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,28 +3423,31 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-75200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-61700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-54800</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
+      <c r="H76" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-9800</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -3270,20 +3455,23 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
         <v>105800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-72100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3">
-        <v>0</v>
+      <c r="L81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M81" s="3">
         <v>0</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,31 +3624,32 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3468,8 +3666,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,35 +3886,38 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2700</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3714,8 +3930,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,31 +3950,32 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3772,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,31 +4144,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3953,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,35 +4318,38 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>6600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2900</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4117,31 +4362,34 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4158,35 +4406,38 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,6 +4448,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCEA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>OCEA</t>
   </si>
@@ -656,80 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -754,14 +766,14 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -772,8 +784,17 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +837,17 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +890,17 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +917,64 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="M12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <v>3200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,52 +1017,70 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="J14" s="3">
         <v>14000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1123,17 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1147,117 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>700</v>
+      </c>
+      <c r="F17" s="3">
+        <v>600</v>
+      </c>
+      <c r="G17" s="3">
         <v>-700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>2700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>2800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>5400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>-5400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-6900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,85 +1274,97 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="G20" s="3">
         <v>17000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3">
         <v>10900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="I20" s="3">
         <v>7000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="J20" s="3">
         <v>52500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>13600</v>
+      </c>
+      <c r="G21" s="3">
         <v>-16400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="H21" s="3">
         <v>-13600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="I21" s="3">
         <v>-9900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="J21" s="3">
         <v>-57800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="K21" s="3">
         <v>100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="L21" s="3">
         <v>-3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="M21" s="3">
         <v>-7300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1263,8 +1374,17 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1272,87 +1392,105 @@
         <v>500</v>
       </c>
       <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>600</v>
+      </c>
+      <c r="G22" s="3">
+        <v>500</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F23" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G23" s="3">
         <v>-16900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>-14100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>-11400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>-72100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-7300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>-5400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1377,14 +1515,14 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1395,8 +1533,17 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1586,123 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F26" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-16900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>-14100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>-11400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>-72100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F27" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-16900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>-14100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>-11400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>-72100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>-7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>-5400</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1745,17 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1798,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1851,17 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1904,123 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-17000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3">
         <v>-10900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="I32" s="3">
         <v>-7000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="J32" s="3">
         <v>-52500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F33" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-16900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>-14100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>-11400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>-72100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>-5400</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +2063,128 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F35" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-16900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>-14100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>-11400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>-72100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>-5400</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2201,11 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2222,64 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>0</v>
+      <c r="D41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,8 +2322,17 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2078,26 +2357,35 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3">
+        <v>0</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2122,14 +2410,14 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2140,8 +2428,17 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2157,94 +2454,112 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G46" s="3">
         <v>2100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>1000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>2200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>1800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>1100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3">
         <v>1800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>600</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G47" s="3">
         <v>3400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,26 +2569,35 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2298,14 +2622,14 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2316,8 +2640,17 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2693,17 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2746,17 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2799,17 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2474,26 +2834,35 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>107100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2905,70 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G54" s="3">
         <v>5500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>1000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>2200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>1800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>1100</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3">
         <v>108900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2985,11 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,8 +3006,11 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2625,31 +3018,31 @@
         <v>900</v>
       </c>
       <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>900</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>10000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2657,43 +3050,52 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G58" s="3">
         <v>13100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>13300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>13100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>8000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2704,29 +3106,38 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2736,8 +3147,8 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
@@ -2745,43 +3156,52 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F60" s="3">
+        <v>30100</v>
+      </c>
+      <c r="G60" s="3">
         <v>30000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>30900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>29800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>23700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>12700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>11000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
@@ -2789,32 +3209,41 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F61" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G61" s="3">
         <v>4100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>3800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>3500</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2836,52 +3265,70 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>59100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>44200</v>
+      </c>
+      <c r="G62" s="3">
         <v>62100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>41600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>30500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>31300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3371,17 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3424,17 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3477,70 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>94600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>78700</v>
+      </c>
+      <c r="G66" s="3">
         <v>96300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>76300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>63800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>55100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>12700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>11000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3557,11 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3604,17 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3657,17 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3710,17 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,40 +3763,49 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-205800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-200300</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-183100</v>
+      </c>
+      <c r="G72" s="3">
         <v>-196100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>-179200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>-165100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>-153700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>-81600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-80600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
-        <v>0</v>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
@@ -3291,11 +3813,20 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3869,17 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3922,17 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3975,70 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-98100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-92700</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-75800</v>
+      </c>
+      <c r="G76" s="3">
         <v>-90800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>-75200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>-61700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>-54800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>-10800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>-9800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3">
         <v>105800</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +4081,128 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F81" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-16900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>-14100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>-11400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>-72100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>-5400</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +4219,11 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3651,14 +4248,14 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3669,8 +4266,17 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4319,17 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4372,17 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4425,17 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4478,17 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,8 +4531,17 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3898,43 +4549,52 @@
         <v>-900</v>
       </c>
       <c r="E89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-4800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4611,11 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3977,14 +4640,14 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3995,8 +4658,17 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4711,17 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,8 +4764,17 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4109,26 +4799,35 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4844,11 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,14 +4873,14 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4189,8 +4891,17 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4944,17 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4997,17 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +5050,70 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>6600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>2900</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,14 +5138,14 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4409,8 +5156,17 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4418,39 +5174,48 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
